--- a/artfynd/A 58919-2021 artfynd.xlsx
+++ b/artfynd/A 58919-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58919-2021 artfynd.xlsx
+++ b/artfynd/A 58919-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3385,125 +3385,6 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>113266166</v>
-      </c>
-      <c r="B23" t="n">
-        <v>90330</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>1110</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tallharticka</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Pelloporus triqueter</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Pers.) Quél.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Bottorp 3:1, Sm</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>572367</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6272139</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Ljungby</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2023-11-15</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2023-11-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Återfynd ny fruktkropp. Första fynd 2021. Ingen fk 2022</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58919-2021 artfynd.xlsx
+++ b/artfynd/A 58919-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97156990</v>
+        <v>97350040</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91907</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1110</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallharticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus triqueter</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572762.201769633</v>
+        <v>572367</v>
       </c>
       <c r="R2" t="n">
-        <v>6272099.802716584</v>
+        <v>6272139</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,27 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-29</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>avverkningsanmälan 58919-2021</t>
+          <t>Äldre fruktkropp ca 5x5cm på tallstubbe 20 meter SO om stigen. Avverkningsanmälan A 58919-2021.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,51 +781,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97156953</v>
+        <v>97350042</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -857,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572774.671157641</v>
+        <v>572432</v>
       </c>
       <c r="R3" t="n">
-        <v>6272048.800418681</v>
+        <v>6272038</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,27 +849,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-29</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>avverkningsanmälan 58919-2021</t>
+          <t>A 58919-2021</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97156755</v>
+        <v>134020680</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -951,49 +898,54 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100070</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bottorp 3:1, Sm</t>
+          <t>Vassmolösa, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572665.0294002304</v>
+        <v>572394</v>
       </c>
       <c r="R4" t="n">
-        <v>6272102.532178374</v>
+        <v>6271930</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,32 +964,17 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Ljungby</t>
+          <t>Hagby</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan 58919-2021</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,27 +990,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Lucia Caroli</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Lucia Caroli, Tobias Uller, Tyra Westelius</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>97156970</v>
+        <v>134020681</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,49 +1017,54 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100070</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bottorp 3:1, Sm</t>
+          <t>Vassmolösa, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572771.4944725344</v>
+        <v>572402</v>
       </c>
       <c r="R5" t="n">
-        <v>6272072.977618886</v>
+        <v>6271920</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1142,32 +1083,17 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Ljungby</t>
+          <t>Hagby</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan 58919-2021</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1183,27 +1109,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Lucia Caroli</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Lucia Caroli, Tobias Uller, Tyra Westelius</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97156889</v>
+        <v>97156755</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1155,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1247,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572770.0857309606</v>
+        <v>572665</v>
       </c>
       <c r="R6" t="n">
-        <v>6271994.749382225</v>
+        <v>6272103</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1280,19 +1205,9 @@
           <t>2021-11-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1325,15 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97156905</v>
+        <v>97156810</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1270,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1377,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572781.9283843646</v>
+        <v>572675</v>
       </c>
       <c r="R7" t="n">
-        <v>6272012.026657844</v>
+        <v>6272064</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1410,19 +1320,9 @@
           <t>2021-11-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1455,15 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97157054</v>
+        <v>97156748</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1385,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1507,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572744.1292122974</v>
+        <v>572696</v>
       </c>
       <c r="R8" t="n">
-        <v>6272091.780646832</v>
+        <v>6272124</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1540,19 +1435,9 @@
           <t>2021-11-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1585,15 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97156922</v>
+        <v>97156819</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,7 +1500,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1637,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572799.2401453395</v>
+        <v>572726</v>
       </c>
       <c r="R9" t="n">
-        <v>6272000.209427969</v>
+        <v>6272030</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1670,19 +1550,9 @@
           <t>2021-11-14</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1715,15 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97156819</v>
+        <v>97156829</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1615,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1767,10 +1632,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572725.8936346362</v>
+        <v>572713</v>
       </c>
       <c r="R10" t="n">
-        <v>6272029.233696716</v>
+        <v>6271986</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1800,19 +1665,9 @@
           <t>2021-11-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1845,15 +1700,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97156950</v>
+        <v>97156840</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1897,10 +1747,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572785.7715256244</v>
+        <v>572729</v>
       </c>
       <c r="R11" t="n">
-        <v>6272045.136971882</v>
+        <v>6271970</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1930,19 +1780,9 @@
           <t>2021-11-14</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1975,15 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>97156810</v>
+        <v>97156844</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2010,7 +1845,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2027,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572675.6336877145</v>
+        <v>572749</v>
       </c>
       <c r="R12" t="n">
-        <v>6272063.613538262</v>
+        <v>6271985</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2060,19 +1895,9 @@
           <t>2021-11-14</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2105,15 +1930,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>97156829</v>
+        <v>97156886</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2140,7 +1960,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2157,10 +1977,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572712.2903999385</v>
+        <v>572761</v>
       </c>
       <c r="R13" t="n">
-        <v>6271986.041692746</v>
+        <v>6271966</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2190,19 +2010,9 @@
           <t>2021-11-14</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2235,15 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>97156886</v>
+        <v>97156889</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2270,7 +2075,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2287,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572761.7527616464</v>
+        <v>572770</v>
       </c>
       <c r="R14" t="n">
-        <v>6271965.967118665</v>
+        <v>6271995</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2320,19 +2125,9 @@
           <t>2021-11-14</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2365,15 +2160,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97156914</v>
+        <v>97156905</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2400,7 +2190,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2417,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572796.7766272058</v>
+        <v>572782</v>
       </c>
       <c r="R15" t="n">
-        <v>6272015.036736673</v>
+        <v>6272012</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2450,19 +2240,9 @@
           <t>2021-11-14</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2495,15 +2275,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>97156840</v>
+        <v>97156914</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2530,7 +2305,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2547,10 +2322,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572729.6875604289</v>
+        <v>572797</v>
       </c>
       <c r="R16" t="n">
-        <v>6271969.268924934</v>
+        <v>6272015</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2580,19 +2355,9 @@
           <t>2021-11-14</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2625,15 +2390,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>97156977</v>
+        <v>97156922</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2677,10 +2437,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572775.1471610969</v>
+        <v>572799</v>
       </c>
       <c r="R17" t="n">
-        <v>6272085.156653318</v>
+        <v>6272000</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2710,19 +2470,9 @@
           <t>2021-11-14</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2755,15 +2505,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>97156844</v>
+        <v>97156930</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2790,7 +2535,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2807,10 +2552,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572748.1888476257</v>
+        <v>572802</v>
       </c>
       <c r="R18" t="n">
-        <v>6271984.458142218</v>
+        <v>6272043</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2840,19 +2585,9 @@
           <t>2021-11-14</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2885,15 +2620,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>97156930</v>
+        <v>97156950</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2920,7 +2650,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2937,10 +2667,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572801.8086133112</v>
+        <v>572785</v>
       </c>
       <c r="R19" t="n">
-        <v>6272043.211004899</v>
+        <v>6272045</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2970,19 +2700,9 @@
           <t>2021-11-14</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3015,15 +2735,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>97156959</v>
+        <v>97156953</v>
       </c>
       <c r="B20" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3050,7 +2765,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3067,10 +2782,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572748.7321806236</v>
+        <v>572774</v>
       </c>
       <c r="R20" t="n">
-        <v>6272048.903387395</v>
+        <v>6272049</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3100,19 +2815,9 @@
           <t>2021-11-14</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3145,42 +2850,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>97350042</v>
+        <v>97156959</v>
       </c>
       <c r="B21" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3188,10 +2897,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>572431.6044063761</v>
+        <v>572748</v>
       </c>
       <c r="R21" t="n">
-        <v>6272037.934716318</v>
+        <v>6272049</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3218,27 +2927,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-11-29</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-11-29</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-14</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>A 58919-2021</t>
+          <t>avverkningsanmälan 58919-2021</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3266,42 +2965,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>97350040</v>
+        <v>97156970</v>
       </c>
       <c r="B22" t="n">
-        <v>89390</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1110</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallharticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus triqueter</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3309,10 +3012,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>572366.4016660374</v>
+        <v>572771</v>
       </c>
       <c r="R22" t="n">
-        <v>6272139.249188751</v>
+        <v>6272073</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3339,27 +3042,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2021-11-29</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2021-11-29</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-14</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre fruktkropp ca 5x5cm på tallstubbe 20 meter SO om stigen. Avverkningsanmälan A 58919-2021.</t>
+          <t>avverkningsanmälan 58919-2021</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3384,6 +3077,351 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>97156977</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bottorp 3:1, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>572775</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6272085</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2021-11-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2021-11-14</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan 58919-2021</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>97156990</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bottorp 3:1, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>572762</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6272100</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2021-11-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2021-11-14</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan 58919-2021</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>97157054</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bottorp 3:1, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>572744</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6272092</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2021-11-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2021-11-14</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan 58919-2021</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58919-2021 artfynd.xlsx
+++ b/artfynd/A 58919-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97350040</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97350042</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
           <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134020680</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
           <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134020681</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156748</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1352,6 +1382,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156755</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1467,6 +1502,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156810</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1582,6 +1622,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156819</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1697,6 +1742,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156829</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1812,6 +1862,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156840</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1927,6 +1982,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156844</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2042,6 +2102,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156886</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2157,6 +2222,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156889</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2272,6 +2342,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156905</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2387,6 +2462,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156914</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2502,6 +2582,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156922</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2617,6 +2702,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156930</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2732,6 +2822,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156950</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2847,6 +2942,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156953</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2962,6 +3062,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156959</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3077,6 +3182,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156970</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3192,6 +3302,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156977</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3307,6 +3422,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156990</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3422,8 +3542,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97157054</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>